--- a/data/trans_camb/P16A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,73</t>
+          <t>0,86; 8,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,44</t>
+          <t>2,25; 9,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 18,85</t>
+          <t>10,28; 19,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 17,51</t>
+          <t>8,52; 17,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 16,69</t>
+          <t>7,69; 17,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 24,31</t>
+          <t>15,4; 23,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,76</t>
+          <t>5,56; 11,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,51</t>
+          <t>6,25; 12,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,62</t>
+          <t>14,48; 20,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 78,58</t>
+          <t>5,99; 80,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 95,86</t>
+          <t>15,4; 93,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,25; 172,37</t>
+          <t>69,6; 179,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,41; 98,45</t>
+          <t>38,44; 100,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,43; 92,79</t>
+          <t>33,39; 95,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,54; 137,11</t>
+          <t>70,13; 139,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 77,54</t>
+          <t>30,69; 77,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,94; 82,8</t>
+          <t>34,69; 83,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,28; 135,61</t>
+          <t>80,6; 139,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,15</t>
+          <t>2,38; 8,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,94</t>
+          <t>2,79; 9,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 9,76</t>
+          <t>-5,58; 9,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 13,52</t>
+          <t>5,7; 13,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,58</t>
+          <t>2,54; 10,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,72; 21,53</t>
+          <t>13,57; 21,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,41</t>
+          <t>5,18; 10,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,12</t>
+          <t>3,92; 9,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 13,87</t>
+          <t>-0,35; 13,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 78,93</t>
+          <t>15,71; 75,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 86,0</t>
+          <t>17,56; 83,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 75,38</t>
+          <t>-38,73; 76,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,81; 65,52</t>
+          <t>23,57; 68,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 52,55</t>
+          <t>10,82; 52,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,91; 108,84</t>
+          <t>55,53; 108,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,92; 62,96</t>
+          <t>26,97; 63,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,64; 56,21</t>
+          <t>20,96; 56,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 81,97</t>
+          <t>2,01; 81,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,75</t>
+          <t>0,12; 8,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,18</t>
+          <t>-0,9; 6,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 15,3</t>
+          <t>6,48; 15,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,62</t>
+          <t>1,07; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 7,21</t>
+          <t>-2,16; 6,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 47,41</t>
+          <t>8,48; 50,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,09</t>
+          <t>1,95; 8,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,64</t>
+          <t>-0,29; 5,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 40,08</t>
+          <t>9,5; 39,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 74,86</t>
+          <t>-0,41; 74,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 61,91</t>
+          <t>-7,29; 62,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,25; 149,15</t>
+          <t>45,39; 146,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 45,51</t>
+          <t>3,84; 43,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 30,13</t>
+          <t>-7,68; 29,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 200,45</t>
+          <t>31,73; 208,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 46,75</t>
+          <t>9,16; 47,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 31,88</t>
+          <t>-1,39; 33,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,66; 215,65</t>
+          <t>48,03; 218,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,68</t>
+          <t>-2,1; 4,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,78</t>
+          <t>0,77; 7,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,41</t>
+          <t>4,94; 12,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,04</t>
+          <t>6,03; 14,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,23</t>
+          <t>3,59; 11,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 16,04</t>
+          <t>3,8; 16,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,75</t>
+          <t>3,39; 8,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,3</t>
+          <t>3,56; 8,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,31</t>
+          <t>6,75; 13,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 31,04</t>
+          <t>-11,6; 33,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 50,23</t>
+          <t>4,24; 52,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,79; 82,51</t>
+          <t>24,55; 81,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,74; 55,96</t>
+          <t>20,98; 57,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,96; 48,42</t>
+          <t>12,44; 48,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,8; 64,04</t>
+          <t>15,5; 64,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,44; 41,6</t>
+          <t>14,76; 43,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,65; 43,85</t>
+          <t>15,54; 43,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,28; 64,63</t>
+          <t>30,85; 64,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,74</t>
+          <t>2,18; 5,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,7</t>
+          <t>3,12; 6,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,11</t>
+          <t>2,87; 11,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,72</t>
+          <t>7,61; 11,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,19</t>
+          <t>5,14; 9,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,82; 29,23</t>
+          <t>13,41; 27,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,21</t>
+          <t>5,43; 8,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,63</t>
+          <t>4,7; 7,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,12</t>
+          <t>10,04; 19,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,09; 43,93</t>
+          <t>14,62; 45,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21,14; 50,37</t>
+          <t>20,98; 51,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27,65; 84,54</t>
+          <t>22,65; 84,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,33; 50,89</t>
+          <t>30,47; 53,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,12; 40,06</t>
+          <t>20,29; 41,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,71; 123,79</t>
+          <t>55,0; 116,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,83; 45,22</t>
+          <t>27,83; 45,4</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24,07; 41,73</t>
+          <t>23,57; 41,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52,09; 105,95</t>
+          <t>50,89; 102,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>14,78</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,95</t>
+          <t>19,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,48</t>
+          <t>17,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,69</t>
+          <t>0,73; 8,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,99</t>
+          <t>2,1; 10,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,24</t>
+          <t>10,46; 19,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,63</t>
+          <t>8,26; 17,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 17,33</t>
+          <t>8,01; 17,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,4; 23,95</t>
+          <t>15,0; 23,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,87</t>
+          <t>6,16; 11,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,71</t>
+          <t>6,33; 12,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 20,98</t>
+          <t>13,99; 20,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114,64%</t>
+          <t>116,09%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>106,45%</t>
+          <t>105,35%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 80,95</t>
+          <t>4,44; 73,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 93,78</t>
+          <t>13,98; 91,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,6; 179,49</t>
+          <t>72,3; 167,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,44; 100,89</t>
+          <t>36,06; 96,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 95,12</t>
+          <t>36,27; 99,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,13; 139,19</t>
+          <t>68,32; 132,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 77,89</t>
+          <t>34,29; 79,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,69; 83,79</t>
+          <t>35,13; 83,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,6; 139,3</t>
+          <t>77,93; 135,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,37</t>
+          <t>17,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>12,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,99</t>
+          <t>2,31; 8,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,99</t>
+          <t>3,09; 9,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 9,49</t>
+          <t>4,75; 11,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,86</t>
+          <t>6,07; 14,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,58</t>
+          <t>2,6; 10,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,42</t>
+          <t>13,03; 20,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,39</t>
+          <t>5,03; 10,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,18</t>
+          <t>3,71; 8,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 13,81</t>
+          <t>10,15; 15,45</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,71; 75,87</t>
+          <t>14,43; 75,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 83,12</t>
+          <t>19,97; 77,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 76,19</t>
+          <t>31,72; 99,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,57; 68,22</t>
+          <t>24,49; 70,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 52,26</t>
+          <t>11,13; 51,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,53; 108,3</t>
+          <t>54,36; 103,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 63,21</t>
+          <t>25,99; 61,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 56,66</t>
+          <t>18,8; 53,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 81,35</t>
+          <t>52,28; 94,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>10,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,34</t>
+          <t>10,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,02</t>
+          <t>0,57; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,38</t>
+          <t>-0,91; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,31</t>
+          <t>6,2; 14,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,48</t>
+          <t>0,66; 10,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,86</t>
+          <t>-2,2; 7,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 50,74</t>
+          <t>5,53; 14,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,26</t>
+          <t>1,84; 8,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,89</t>
+          <t>-0,46; 5,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,5; 39,67</t>
+          <t>7,37; 13,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>101,07%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 74,06</t>
+          <t>2,47; 72,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 62,01</t>
+          <t>-6,63; 55,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,39; 146,72</t>
+          <t>43,94; 139,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 43,74</t>
+          <t>2,18; 46,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 29,43</t>
+          <t>-7,92; 31,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,73; 208,35</t>
+          <t>19,58; 64,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 47,62</t>
+          <t>8,61; 46,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 33,67</t>
+          <t>-2,32; 30,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,03; 218,81</t>
+          <t>34,97; 76,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>10,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,98</t>
+          <t>-1,85; 5,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,78</t>
+          <t>1,17; 8,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,48</t>
+          <t>4,52; 11,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,16</t>
+          <t>5,69; 13,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,98</t>
+          <t>3,79; 11,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,16</t>
+          <t>9,67; 17,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,9</t>
+          <t>3,21; 9,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,82</t>
+          <t>3,46; 9,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 13,22</t>
+          <t>8,33; 13,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 33,27</t>
+          <t>-10,13; 35,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 52,46</t>
+          <t>5,35; 53,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,55; 81,26</t>
+          <t>24,51; 79,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,98; 57,4</t>
+          <t>19,7; 55,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 48,89</t>
+          <t>13,16; 48,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,5; 64,91</t>
+          <t>33,24; 70,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,76; 43,86</t>
+          <t>13,59; 44,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,54; 43,53</t>
+          <t>14,86; 43,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,85; 64,21</t>
+          <t>35,87; 67,42</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,07</t>
+          <t>15,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,96</t>
+          <t>2,13; 5,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,8</t>
+          <t>3,32; 6,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,23</t>
+          <t>7,87; 12,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,95</t>
+          <t>7,47; 12,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,51</t>
+          <t>5,04; 9,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,41; 27,81</t>
+          <t>13,09; 17,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,31</t>
+          <t>5,36; 8,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,62</t>
+          <t>4,73; 7,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,45</t>
+          <t>11,32; 14,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,62; 45,72</t>
+          <t>14,67; 44,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20,98; 51,52</t>
+          <t>22,1; 50,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22,65; 84,33</t>
+          <t>54,15; 92,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,47; 53,22</t>
+          <t>29,9; 53,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,29; 41,24</t>
+          <t>20,26; 41,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,0; 116,79</t>
+          <t>52,58; 75,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,83; 45,4</t>
+          <t>27,44; 45,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23,57; 41,77</t>
+          <t>23,71; 41,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,89; 102,13</t>
+          <t>57,45; 77,62</t>
         </is>
       </c>
     </row>
